--- a/media/ViewUploadedBills/Verizon_July_2025.xlsx
+++ b/media/ViewUploadedBills/Verizon_July_2025.xlsx
@@ -454,92 +454,86 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="6" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="27" customWidth="1" min="13" max="13"/>
-    <col width="46" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="27" customWidth="1" min="12" max="12"/>
+    <col width="46" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>Organization</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Sub Company</t>
+          <t>Vendor</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Remittance Address</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Remittance Address</t>
+          <t>Account Number</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Account Number</t>
+          <t>Invoice Number</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Invoice Number</t>
+          <t>Bill Date</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Bill Date</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Year</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Year</t>
+          <t>Total Amount</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Total Amount</t>
+          <t>Due Date</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Due Date</t>
+          <t>Billing Name</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Billing Name</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Billing Address</t>
         </is>
@@ -548,70 +542,65 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>OneSmarter</t>
+          <t>OSI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>OSI</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
           <t>Verizon</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>http://sso.verizonenterprise.com</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PO BOX 489 NEWARK, NJ 07101-0489</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PO BOX 489 NEWARK, NJ 07101-0489</t>
+          <t>342125539-00001</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>342125539-00001</t>
+          <t>6118585051</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>6118585051</t>
+          <t>July 15 2025</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>July 15 2025</t>
+          <t>July</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>$2,704.51</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>$2,704.51</t>
+          <t>August 14 2025</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>August 14 2025</t>
+          <t>BUILD-A-BEAR WORKSHOP INC</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
-        <is>
-          <t>BUILD-A-BEAR WORKSHOP INC</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
         <is>
           <t>7293 BEECHMONT AVE CINCINNATI, OH 45230-4125</t>
         </is>
@@ -619,7 +608,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
